--- a/Stundenliste_neu(1)(1).xlsx
+++ b/Stundenliste_neu(1)(1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VR1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arthur\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35368EC8-B302-4C89-B38E-366B4EB55E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48DED62-4433-4645-ADF9-313775B712CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="28800" windowHeight="15435" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{904973F5-B02B-4666-A03D-BB66738E721E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="101">
   <si>
     <t>Tag</t>
   </si>
@@ -321,6 +321,24 @@
   </si>
   <si>
     <t>Diplo schreiben</t>
+  </si>
+  <si>
+    <t>Projekt reparieren</t>
+  </si>
+  <si>
+    <t>Schreiben + Müllberg Szene</t>
+  </si>
+  <si>
+    <t>Müllberg-Szene</t>
+  </si>
+  <si>
+    <t>Schreiben</t>
+  </si>
+  <si>
+    <t>Terrain-Materials verbessert</t>
+  </si>
+  <si>
+    <t>3D-Modelle + Materials +  Texturen für  Szenen</t>
   </si>
 </sst>
 </file>
@@ -457,8 +475,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -675,7 +693,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -837,7 +855,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.91557017543859187</c:v>
+                  <c:v>0.93475877192981971</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -937,7 +955,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.76754385964911886</c:v>
+                  <c:v>0.87445175438596034</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1037,7 +1055,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.73190789473683837</c:v>
+                  <c:v>0.75109649122806621</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1945,10 +1963,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G86" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:G86" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G80">
-    <sortCondition ref="B1:B80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CD71F5EC-BCBD-4D95-9F21-060EF7779827}" name="Stundenliste" displayName="Stundenliste" ref="A1:G93" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:G93" xr:uid="{730AE997-56E9-481C-8C9C-45C7D9E3EFFC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G93">
+    <sortCondition ref="B1:B93"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{AD59871A-76CC-45F6-8F91-44F7ED02573E}" name="Tag" dataDxfId="14">
@@ -2004,9 +2022,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2044,7 +2062,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2150,7 +2168,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2301,8 +2319,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{730198CE-52B5-4F02-9B4B-1774B163D30B}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:Q86"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q93"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
@@ -2338,7 +2356,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
-        <f t="shared" ref="A2:A33" si="0">IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
+        <f>IF(ISNUMBER(B2),LEFT(TEXT(B2,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B2" s="3">
@@ -2387,7 +2405,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B3),LEFT(TEXT(B3,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B3" s="3">
@@ -2422,28 +2440,28 @@
       </c>
       <c r="M3" s="11">
         <f>SUM(J4,J7,J8,J11)</f>
-        <v>6.9583333333333339</v>
+        <v>7.104166666666667</v>
       </c>
       <c r="N3" s="18">
         <f>M3</f>
-        <v>6.9583333333333339</v>
+        <v>7.104166666666667</v>
       </c>
       <c r="O3" s="18">
         <f>N3/60</f>
-        <v>0.11597222222222223</v>
+        <v>0.11840277777777779</v>
       </c>
       <c r="P3" s="22">
-        <f t="shared" ref="P3:P6" si="1">(O3/180)*100</f>
-        <v>6.4429012345679021E-2</v>
+        <f t="shared" ref="P3:P6" si="0">(O3/180)*100</f>
+        <v>6.5779320987654322E-2</v>
       </c>
       <c r="Q3" s="21">
         <f>(P3*1421.05263157894)/100</f>
-        <v>0.91557017543859187</v>
+        <v>0.93475877192981971</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B4),LEFT(TEXT(B4,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B4" s="3">
@@ -2477,28 +2495,28 @@
       </c>
       <c r="M4" s="11">
         <f>SUM(J5,J8,J9,J11)</f>
-        <v>5.8333333333333339</v>
+        <v>6.645833333333333</v>
       </c>
       <c r="N4" s="18">
-        <f t="shared" ref="N4:N5" si="2">M4</f>
-        <v>5.8333333333333339</v>
+        <f t="shared" ref="N4:N5" si="1">M4</f>
+        <v>6.645833333333333</v>
       </c>
       <c r="O4" s="18">
-        <f t="shared" ref="O4:O5" si="3">N4/60</f>
-        <v>9.7222222222222238E-2</v>
+        <f t="shared" ref="O4:O5" si="2">N4/60</f>
+        <v>0.11076388888888888</v>
       </c>
       <c r="P4" s="22">
-        <f t="shared" si="1"/>
-        <v>5.401234567901235E-2</v>
+        <f t="shared" si="0"/>
+        <v>6.153549382716049E-2</v>
       </c>
       <c r="Q4" s="21">
-        <f t="shared" ref="Q4:Q5" si="4">(P4*1421.05263157894)/100</f>
-        <v>0.76754385964911886</v>
+        <f t="shared" ref="Q4:Q5" si="3">(P4*1421.05263157894)/100</f>
+        <v>0.87445175438596034</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B5),LEFT(TEXT(B5,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B5" s="3">
@@ -2525,35 +2543,35 @@
       </c>
       <c r="J5" s="10">
         <f>SUMIF(Stundenliste[Wer],I5,Stundenliste[Stunden])</f>
-        <v>1.7708333333333335</v>
+        <v>2.4375</v>
       </c>
       <c r="L5" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="11">
         <f>SUM(J3,J7,J9,J11)</f>
-        <v>5.5625</v>
+        <v>5.7083333333333321</v>
       </c>
       <c r="N5" s="18">
+        <f t="shared" si="1"/>
+        <v>5.7083333333333321</v>
+      </c>
+      <c r="O5" s="18">
         <f t="shared" si="2"/>
-        <v>5.5625</v>
-      </c>
-      <c r="O5" s="18">
+        <v>9.513888888888887E-2</v>
+      </c>
+      <c r="P5" s="22">
+        <f t="shared" si="0"/>
+        <v>5.285493827160493E-2</v>
+      </c>
+      <c r="Q5" s="21">
         <f t="shared" si="3"/>
-        <v>9.2708333333333337E-2</v>
-      </c>
-      <c r="P5" s="22">
-        <f t="shared" si="1"/>
-        <v>5.1504629629629629E-2</v>
-      </c>
-      <c r="Q5" s="21">
-        <f t="shared" si="4"/>
-        <v>0.73190789473683837</v>
+        <v>0.75109649122806621</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B6),LEFT(TEXT(B6,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B6" s="3">
@@ -2586,7 +2604,7 @@
         <v>180</v>
       </c>
       <c r="P6" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="Q6" s="21">
@@ -2596,7 +2614,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B7),LEFT(TEXT(B7,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B7" s="3">
@@ -2626,8 +2644,8 @@
         <v>0.77083333333333326</v>
       </c>
       <c r="M7" s="15">
-        <f>SUM(F2:F86)</f>
-        <v>10.250000000000005</v>
+        <f>SUM(F2:F93)</f>
+        <v>11.062500000000007</v>
       </c>
       <c r="N7">
         <v>180</v>
@@ -2635,7 +2653,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B8),LEFT(TEXT(B8,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B8" s="3">
@@ -2666,12 +2684,12 @@
       </c>
       <c r="M8" s="16">
         <f>TEXT(M7,"[h]")+TEXT(M7,"mm")/60</f>
-        <v>246</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B9),LEFT(TEXT(B9,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B9" s="3">
@@ -2703,7 +2721,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B10),LEFT(TEXT(B10,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B10" s="3">
@@ -2730,7 +2748,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B11),LEFT(TEXT(B11,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B11" s="3">
@@ -2757,12 +2775,12 @@
       </c>
       <c r="J11" s="10">
         <f>SUMIF(Stundenliste[Wer],I11,Stundenliste[Stunden])</f>
-        <v>3.2708333333333335</v>
+        <v>3.4166666666666661</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B12),LEFT(TEXT(B12,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B12" s="3">
@@ -2787,7 +2805,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B13),LEFT(TEXT(B13,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B13" s="3">
@@ -2815,7 +2833,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B14),LEFT(TEXT(B14,"TTTT"),2)&amp;".","")</f>
         <v>Mo.</v>
       </c>
       <c r="B14" s="3">
@@ -2843,7 +2861,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B15),LEFT(TEXT(B15,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B15" s="3">
@@ -2868,7 +2886,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B16),LEFT(TEXT(B16,"TTTT"),2)&amp;".","")</f>
         <v>Do.</v>
       </c>
       <c r="B16" s="3">
@@ -2893,7 +2911,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B17),LEFT(TEXT(B17,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B17" s="3">
@@ -2918,7 +2936,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B18),LEFT(TEXT(B18,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B18" s="3">
@@ -2943,7 +2961,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B19),LEFT(TEXT(B19,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B19" s="3">
@@ -2968,7 +2986,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B20),LEFT(TEXT(B20,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B20" s="3">
@@ -2993,7 +3011,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B21),LEFT(TEXT(B21,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B21" s="3">
@@ -3018,7 +3036,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B22),LEFT(TEXT(B22,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B22" s="3">
@@ -3043,7 +3061,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B23),LEFT(TEXT(B23,"TTTT"),2)&amp;".","")</f>
         <v>Do.</v>
       </c>
       <c r="B23" s="3">
@@ -3068,7 +3086,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B24),LEFT(TEXT(B24,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B24" s="3">
@@ -3093,7 +3111,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B25),LEFT(TEXT(B25,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B25" s="3">
@@ -3118,7 +3136,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B26),LEFT(TEXT(B26,"TTTT"),2)&amp;".","")</f>
         <v>Do.</v>
       </c>
       <c r="B26" s="3">
@@ -3143,7 +3161,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B27),LEFT(TEXT(B27,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B27" s="3">
@@ -3168,7 +3186,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B28),LEFT(TEXT(B28,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B28" s="3">
@@ -3193,7 +3211,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B29),LEFT(TEXT(B29,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B29" s="3">
@@ -3218,7 +3236,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B30),LEFT(TEXT(B30,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B30" s="3">
@@ -3243,7 +3261,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B31),LEFT(TEXT(B31,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B31" s="3">
@@ -3268,7 +3286,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B32),LEFT(TEXT(B32,"TTTT"),2)&amp;".","")</f>
         <v>Mo.</v>
       </c>
       <c r="B32" s="3">
@@ -3293,7 +3311,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISNUMBER(B33),LEFT(TEXT(B33,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B33" s="3">
@@ -3318,7 +3336,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
-        <f t="shared" ref="A34:A65" si="5">IF(ISNUMBER(B34),LEFT(TEXT(B34,"TTTT"),2)&amp;".","")</f>
+        <f>IF(ISNUMBER(B34),LEFT(TEXT(B34,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B34" s="3">
@@ -3343,7 +3361,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B35),LEFT(TEXT(B35,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B35" s="3">
@@ -3368,7 +3386,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B36),LEFT(TEXT(B36,"TTTT"),2)&amp;".","")</f>
         <v>Mo.</v>
       </c>
       <c r="B36" s="3">
@@ -3393,7 +3411,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B37),LEFT(TEXT(B37,"TTTT"),2)&amp;".","")</f>
         <v>Mo.</v>
       </c>
       <c r="B37" s="3">
@@ -3418,7 +3436,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B38),LEFT(TEXT(B38,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B38" s="3">
@@ -3443,7 +3461,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B39),LEFT(TEXT(B39,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B39" s="3">
@@ -3468,7 +3486,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B40),LEFT(TEXT(B40,"TTTT"),2)&amp;".","")</f>
         <v>Mo.</v>
       </c>
       <c r="B40" s="3">
@@ -3493,7 +3511,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B41),LEFT(TEXT(B41,"TTTT"),2)&amp;".","")</f>
         <v>Mo.</v>
       </c>
       <c r="B41" s="3">
@@ -3518,7 +3536,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B42),LEFT(TEXT(B42,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B42" s="3">
@@ -3543,7 +3561,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B43),LEFT(TEXT(B43,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B43" s="3">
@@ -3567,150 +3585,150 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>So.</v>
+      <c r="A44" s="23" t="str">
+        <f>IF(ISNUMBER(B44),LEFT(TEXT(B44,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B44" s="3">
-        <v>46026</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>46</v>
+        <v>46025</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>99</v>
       </c>
       <c r="D44" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E44" s="4">
-        <v>0.875</v>
-      </c>
-      <c r="F44" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F44" s="5">
         <f>IF(E44&gt;D44,E44-D44,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D44-E44),""))</f>
-        <v>0.16666666666666663</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B45),LEFT(TEXT(B45,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
       </c>
       <c r="B45" s="3">
-        <v>46031</v>
+        <v>46026</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D45" s="4">
-        <v>0.30902777777777779</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E45" s="4">
-        <v>0.35069444444444442</v>
+        <v>0.875</v>
       </c>
       <c r="F45" s="12">
         <f>IF(E45&gt;D45,E45-D45,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D45-E45),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Fr.</v>
+      <c r="A46" s="23" t="str">
+        <f>IF(ISNUMBER(B46),LEFT(TEXT(B46,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
       </c>
       <c r="B46" s="3">
-        <v>46038</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>50</v>
+        <v>46026</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>100</v>
       </c>
       <c r="D46" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E46" s="4">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="F46" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="F46" s="5">
         <f>IF(E46&gt;D46,E46-D46,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D46-E46),""))</f>
-        <v>0.16666666666666674</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B47),LEFT(TEXT(B47,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B47" s="3">
-        <v>46039</v>
+        <v>46031</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D47" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.30902777777777779</v>
       </c>
       <c r="E47" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.35069444444444442</v>
       </c>
       <c r="F47" s="12">
         <f>IF(E47&gt;D47,E47-D47,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D47-E47),""))</f>
-        <v>0.16666666666666674</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Di.</v>
+        <f>IF(ISNUMBER(B48),LEFT(TEXT(B48,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B48" s="3">
-        <v>46042</v>
+        <v>46038</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D48" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E48" s="17">
-        <v>1</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0.83333333333333337</v>
       </c>
       <c r="F48" s="12">
         <f>IF(E48&gt;D48,E48-D48,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D48-E48),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B49),LEFT(TEXT(B49,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B49" s="3">
-        <v>46050</v>
+        <v>46039</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="D49" s="4">
-        <v>0.72222222222222221</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E49" s="4">
-        <v>0.76388888888888884</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F49" s="12">
         <f>IF(E49&gt;D49,E49-D49,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D49-E49),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>0.16666666666666674</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>10</v>
@@ -3718,14 +3736,14 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B50),LEFT(TEXT(B50,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
       </c>
       <c r="B50" s="3">
-        <v>46057</v>
+        <v>46042</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D50" s="4">
         <v>0.91666666666666663</v>
@@ -3743,20 +3761,20 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B51),LEFT(TEXT(B51,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B51" s="3">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="D51" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="E51" s="4">
-        <v>0.75</v>
+        <v>0.76388888888888884</v>
       </c>
       <c r="F51" s="12">
         <f>IF(E51&gt;D51,E51-D51,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D51-E51),""))</f>
@@ -3768,99 +3786,99 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B52),LEFT(TEXT(B52,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B52" s="3">
-        <v>46067</v>
+        <v>46057</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D52" s="4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E52" s="4">
-        <v>0.875</v>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E52" s="17">
+        <v>1</v>
       </c>
       <c r="F52" s="12">
         <f>IF(E52&gt;D52,E52-D52,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D52-E52),""))</f>
-        <v>0.20833333333333337</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B53),LEFT(TEXT(B53,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B53" s="3">
-        <v>46067</v>
+        <v>46062</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D53" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E53" s="4">
         <v>0.75</v>
       </c>
       <c r="F53" s="12">
         <f>IF(E53&gt;D53,E53-D53,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D53-E53),""))</f>
-        <v>0.16666666666666663</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B54),LEFT(TEXT(B54,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B54" s="3">
         <v>46067</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" s="4">
-        <v>0.58333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E54" s="4">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="F54" s="12">
         <f>IF(E54&gt;D54,E54-D54,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D54-E54),""))</f>
-        <v>0.16666666666666663</v>
+        <v>0.20833333333333337</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B55),LEFT(TEXT(B55,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B55" s="3">
-        <v>46073</v>
+        <v>46067</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D55" s="4">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E55" s="4">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F55" s="12">
         <f>IF(E55&gt;D55,E55-D55,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D55-E55),""))</f>
-        <v>0.125</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>9</v>
@@ -3868,49 +3886,49 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B56),LEFT(TEXT(B56,"TTTT"),2)&amp;".","")</f>
         <v>Sa.</v>
       </c>
       <c r="B56" s="3">
-        <v>46074</v>
+        <v>46067</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D56" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E56" s="4">
         <v>0.75</v>
-      </c>
-      <c r="E56" s="4">
-        <v>0</v>
       </c>
       <c r="F56" s="12">
         <f>IF(E56&gt;D56,E56-D56,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D56-E56),""))</f>
-        <v>0.25</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Di.</v>
+        <f>IF(ISNUMBER(B57),LEFT(TEXT(B57,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B57" s="3">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D57" s="4">
-        <v>0.75</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="E57" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="F57" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F57" s="12">
         <f>IF(E57&gt;D57,E57-D57,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D57-E57),""))</f>
-        <v>6.25E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>9</v>
@@ -3918,49 +3936,49 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B58),LEFT(TEXT(B58,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B58" s="3">
-        <v>46080</v>
+        <v>46074</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D58" s="4">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="E58" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F58" s="5">
+        <v>0</v>
+      </c>
+      <c r="F58" s="12">
         <f>IF(E58&gt;D58,E58-D58,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D58-E58),""))</f>
-        <v>4.1666666666666685E-2</v>
+        <v>0.25</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B59),LEFT(TEXT(B59,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
       </c>
       <c r="B59" s="3">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D59" s="4">
-        <v>0.39583333333333331</v>
+        <v>0.75</v>
       </c>
       <c r="E59" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.8125</v>
       </c>
       <c r="F59" s="5">
         <f>IF(E59&gt;D59,E59-D59,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D59-E59),""))</f>
-        <v>2.083333333333337E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>9</v>
@@ -3968,139 +3986,139 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B60),LEFT(TEXT(B60,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B60" s="3">
         <v>46080</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D60" s="4">
-        <v>0.63541666666666663</v>
+        <v>0.375</v>
       </c>
       <c r="E60" s="4">
-        <v>0.69791666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F60" s="5">
         <f>IF(E60&gt;D60,E60-D60,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D60-E60),""))</f>
-        <v>6.25E-2</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B61),LEFT(TEXT(B61,"TTTT"),2)&amp;".","")</f>
         <v>Fr.</v>
       </c>
       <c r="B61" s="3">
         <v>46080</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D61" s="4">
-        <v>0.97916666666666663</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E61" s="4">
-        <v>4.1666666666666664E-2</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F61" s="5">
         <f>IF(E61&gt;D61,E61-D61,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D61-E61),""))</f>
-        <v>6.25E-2</v>
+        <v>2.083333333333337E-2</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B62),LEFT(TEXT(B62,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B62" s="3">
-        <v>46081</v>
+        <v>46080</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D62" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="E62" s="4">
-        <v>0.6875</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="F62" s="5">
         <f>IF(E62&gt;D62,E62-D62,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D62-E62),""))</f>
-        <v>0.27083333333333331</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>So.</v>
+        <f>IF(ISNUMBER(B63),LEFT(TEXT(B63,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B63" s="3">
-        <v>46082</v>
+        <v>46080</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D63" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="E63" s="4">
-        <v>0.70833333333333337</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="F63" s="5">
         <f>IF(E63&gt;D63,E63-D63,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D63-E63),""))</f>
-        <v>0.25000000000000006</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>So.</v>
+        <f>IF(ISNUMBER(B64),LEFT(TEXT(B64,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B64" s="3">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D64" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E64" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="F64" s="5">
         <f>IF(E64&gt;D64,E64-D64,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D64-E64),""))</f>
-        <v>0.25000000000000006</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISNUMBER(B65),LEFT(TEXT(B65,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B65" s="3">
         <v>46082</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D65" s="4">
         <v>0.45833333333333331</v>
@@ -4113,104 +4131,104 @@
         <v>0.25000000000000006</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
-        <f t="shared" ref="A66:A80" si="6">IF(ISNUMBER(B66),LEFT(TEXT(B66,"TTTT"),2)&amp;".","")</f>
+        <f>IF(ISNUMBER(B66),LEFT(TEXT(B66,"TTTT"),2)&amp;".","")</f>
         <v>So.</v>
       </c>
       <c r="B66" s="3">
         <v>46082</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D66" s="4">
-        <v>0.29166666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E66" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F66" s="5">
         <f>IF(E66&gt;D66,E66-D66,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D66-E66),""))</f>
-        <v>0.125</v>
+        <v>0.25000000000000006</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B67),LEFT(TEXT(B67,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
       </c>
       <c r="B67" s="3">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D67" s="4">
-        <v>0.33333333333333331</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E67" s="4">
-        <v>0.375</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F67" s="5">
         <f>IF(E67&gt;D67,E67-D67,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D67-E67),""))</f>
-        <v>4.1666666666666685E-2</v>
+        <v>0.25000000000000006</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B68),LEFT(TEXT(B68,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
       </c>
       <c r="B68" s="3">
-        <v>46083</v>
+        <v>46082</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D68" s="4">
-        <v>0.625</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="E68" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F68" s="5">
         <f>IF(E68&gt;D68,E68-D68,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D68-E68),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Di.</v>
+        <f>IF(ISNUMBER(B69),LEFT(TEXT(B69,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B69" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D69" s="4">
-        <v>0.49305555555555558</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E69" s="4">
-        <v>0.53472222222222221</v>
+        <v>0.375</v>
       </c>
       <c r="F69" s="5">
         <f>IF(E69&gt;D69,E69-D69,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D69-E69),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>7</v>
@@ -4218,14 +4236,14 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Di.</v>
+        <f>IF(ISNUMBER(B70),LEFT(TEXT(B70,"TTTT"),2)&amp;".","")</f>
+        <v>Mo.</v>
       </c>
       <c r="B70" s="3">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D70" s="4">
         <v>0.625</v>
@@ -4243,99 +4261,99 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B71),LEFT(TEXT(B71,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
       </c>
       <c r="B71" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D71" s="4">
-        <v>0.625</v>
+        <v>0.49305555555555558</v>
       </c>
       <c r="E71" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.53472222222222221</v>
       </c>
       <c r="F71" s="5">
         <f>IF(E71&gt;D71,E71-D71,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D71-E71),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Mi.</v>
+        <f>IF(ISNUMBER(B72),LEFT(TEXT(B72,"TTTT"),2)&amp;".","")</f>
+        <v>Di.</v>
       </c>
       <c r="B72" s="3">
-        <v>46085</v>
+        <v>46084</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D72" s="4">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="E72" s="4">
-        <v>0.52777777777777779</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F72" s="5">
         <f>IF(E72&gt;D72,E72-D72,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D72-E72),""))</f>
-        <v>4.1666666666666685E-2</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(ISNUMBER(B73),LEFT(TEXT(B73,"TTTT"),2)&amp;".","")</f>
         <v>Mi.</v>
       </c>
       <c r="B73" s="3">
         <v>46085</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D73" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="E73" s="4">
-        <v>0.91666666666666663</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F73" s="5">
         <f>IF(E73&gt;D73,E73-D73,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D73-E73),""))</f>
-        <v>8.3333333333333259E-2</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Do.</v>
+        <f>IF(ISNUMBER(B74),LEFT(TEXT(B74,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B74" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D74" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="E74" s="4">
-        <v>0.54166666666666663</v>
+        <v>0.52777777777777779</v>
       </c>
       <c r="F74" s="5">
         <f>IF(E74&gt;D74,E74-D74,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D74-E74),""))</f>
-        <v>8.3333333333333315E-2</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>7</v>
@@ -4343,24 +4361,24 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Do.</v>
+        <f>IF(ISNUMBER(B75),LEFT(TEXT(B75,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
       </c>
       <c r="B75" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D75" s="4">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E75" s="4">
-        <v>0.875</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="F75" s="5">
         <f>IF(E75&gt;D75,E75-D75,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D75-E75),""))</f>
-        <v>0.125</v>
+        <v>8.3333333333333259E-2</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>11</v>
@@ -4368,49 +4386,49 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Fr.</v>
+        <f>IF(ISNUMBER(B76),LEFT(TEXT(B76,"TTTT"),2)&amp;".","")</f>
+        <v>Do.</v>
       </c>
       <c r="B76" s="3">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D76" s="4">
-        <v>0.75</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E76" s="4">
-        <v>0.875</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="F76" s="5">
         <f>IF(E76&gt;D76,E76-D76,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D76-E76),""))</f>
-        <v>0.125</v>
+        <v>8.3333333333333315E-2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Sa.</v>
+        <f>IF(ISNUMBER(B77),LEFT(TEXT(B77,"TTTT"),2)&amp;".","")</f>
+        <v>Do.</v>
       </c>
       <c r="B77" s="3">
-        <v>46088</v>
+        <v>46086</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D77" s="4">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="E77" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="F77" s="5">
         <f>IF(E77&gt;D77,E77-D77,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D77-E77),""))</f>
-        <v>8.333333333333337E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>11</v>
@@ -4418,20 +4436,20 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>So.</v>
+        <f>IF(ISNUMBER(B78),LEFT(TEXT(B78,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
       </c>
       <c r="B78" s="3">
-        <v>46089</v>
+        <v>46087</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D78" s="4">
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="E78" s="4">
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="F78" s="5">
         <f>IF(E78&gt;D78,E78-D78,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D78-E78),""))</f>
@@ -4443,49 +4461,49 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B79),LEFT(TEXT(B79,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
       </c>
       <c r="B79" s="3">
-        <v>46090</v>
+        <v>46088</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D79" s="4">
-        <v>0.33333333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="E79" s="4">
-        <v>0.375</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="F79" s="5">
         <f>IF(E79&gt;D79,E79-D79,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D79-E79),""))</f>
-        <v>4.1666666666666685E-2</v>
+        <v>8.333333333333337E-2</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Mo.</v>
+        <f>IF(ISNUMBER(B80),LEFT(TEXT(B80,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
       </c>
       <c r="B80" s="3">
-        <v>46090</v>
+        <v>46089</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D80" s="4">
-        <v>0.375</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="E80" s="4">
-        <v>0.3888888888888889</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="F80" s="5">
         <f>IF(E80&gt;D80,E80-D80,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D80-E80),""))</f>
-        <v>1.3888888888888895E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>11</v>
@@ -4500,81 +4518,81 @@
         <v>46090</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D81" s="4">
-        <v>0.77083333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E81" s="4">
-        <v>0.89583333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="F81" s="5">
         <f>IF(E81&gt;D81,E81-D81,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D81-E81),""))</f>
-        <v>0.125</v>
+        <v>4.1666666666666685E-2</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="23" t="str">
+      <c r="A82" s="2" t="str">
         <f>IF(ISNUMBER(B82),LEFT(TEXT(B82,"TTTT"),2)&amp;".","")</f>
-        <v>Sa.</v>
+        <v>Mo.</v>
       </c>
       <c r="B82" s="3">
-        <v>46095</v>
-      </c>
-      <c r="C82" s="23" t="s">
-        <v>92</v>
+        <v>46090</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="D82" s="4">
-        <v>0.79166666666666663</v>
+        <v>0.375</v>
       </c>
       <c r="E82" s="4">
-        <v>0.95833333333333337</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="F82" s="5">
         <f>IF(E82&gt;D82,E82-D82,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D82-E82),""))</f>
-        <v>0.16666666666666674</v>
+        <v>1.3888888888888895E-2</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="23" t="str">
+      <c r="A83" s="2" t="str">
         <f>IF(ISNUMBER(B83),LEFT(TEXT(B83,"TTTT"),2)&amp;".","")</f>
-        <v>Fr.</v>
+        <v>Mo.</v>
       </c>
       <c r="B83" s="3">
-        <v>46094</v>
-      </c>
-      <c r="C83" s="23" t="s">
-        <v>93</v>
+        <v>46090</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D83" s="4">
-        <v>0.91666666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="E83" s="4">
-        <v>0.125</v>
+        <v>0.89583333333333337</v>
       </c>
       <c r="F83" s="5">
         <f>IF(E83&gt;D83,E83-D83,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D83-E83),""))</f>
-        <v>0.20833333333333337</v>
+        <v>0.125</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="23" t="str">
+      <c r="A84" s="2" t="str">
         <f>IF(ISNUMBER(B84),LEFT(TEXT(B84,"TTTT"),2)&amp;".","")</f>
         <v>Di.</v>
       </c>
       <c r="B84" s="3">
         <v>46091</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D84" s="4">
@@ -4594,52 +4612,217 @@
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="23" t="str">
         <f>IF(ISNUMBER(B85),LEFT(TEXT(B85,"TTTT"),2)&amp;".","")</f>
-        <v>Mi.</v>
+        <v>Di.</v>
       </c>
       <c r="B85" s="3">
-        <v>46092</v>
+        <v>46091</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D85" s="4">
-        <v>0.71875</v>
+        <v>0.625</v>
       </c>
       <c r="E85" s="4">
-        <v>0.76041666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="F85" s="5">
         <f>IF(E85&gt;D85,E85-D85,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D85-E85),""))</f>
-        <v>4.166666666666663E-2</v>
+        <v>0.125</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="23" t="str">
+      <c r="A86" s="2" t="str">
         <f>IF(ISNUMBER(B86),LEFT(TEXT(B86,"TTTT"),2)&amp;".","")</f>
-        <v>Sa.</v>
+        <v>Mi.</v>
       </c>
       <c r="B86" s="3">
-        <v>46095</v>
-      </c>
-      <c r="C86" s="23" t="s">
+        <v>46092</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D86" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.71875</v>
       </c>
       <c r="E86" s="4">
-        <v>0.54166666666666663</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="F86" s="5">
         <f>IF(E86&gt;D86,E86-D86,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D86-E86),""))</f>
-        <v>0.12499999999999994</v>
+        <v>4.166666666666663E-2</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>10</v>
       </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="23" t="str">
+        <f>IF(ISNUMBER(B87),LEFT(TEXT(B87,"TTTT"),2)&amp;".","")</f>
+        <v>Mi.</v>
+      </c>
+      <c r="B87" s="3">
+        <v>46092</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D87" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E87" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F87" s="5">
+        <f>IF(E87&gt;D87,E87-D87,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D87-E87),""))</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="23" t="str">
+        <f>IF(ISNUMBER(B88),LEFT(TEXT(B88,"TTTT"),2)&amp;".","")</f>
+        <v>Do.</v>
+      </c>
+      <c r="B88" s="3">
+        <v>46093</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D88" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F88" s="5">
+        <f>IF(E88&gt;D88,E88-D88,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D88-E88),""))</f>
+        <v>0.125</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="str">
+        <f>IF(ISNUMBER(B89),LEFT(TEXT(B89,"TTTT"),2)&amp;".","")</f>
+        <v>Fr.</v>
+      </c>
+      <c r="B89" s="3">
+        <v>46094</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D89" s="4">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E89" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="F89" s="5">
+        <f>IF(E89&gt;D89,E89-D89,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D89-E89),""))</f>
+        <v>0.20833333333333337</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="str">
+        <f>IF(ISNUMBER(B90),LEFT(TEXT(B90,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
+      </c>
+      <c r="B90" s="3">
+        <v>46095</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D90" s="4">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E90" s="4">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F90" s="5">
+        <f>IF(E90&gt;D90,E90-D90,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D90-E90),""))</f>
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="str">
+        <f>IF(ISNUMBER(B91),LEFT(TEXT(B91,"TTTT"),2)&amp;".","")</f>
+        <v>Sa.</v>
+      </c>
+      <c r="B91" s="3">
+        <v>46095</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E91" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F91" s="5">
+        <f>IF(E91&gt;D91,E91-D91,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D91-E91),""))</f>
+        <v>0.12499999999999994</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="23" t="str">
+        <f>IF(ISNUMBER(B92),LEFT(TEXT(B92,"TTTT"),2)&amp;".","")</f>
+        <v>So.</v>
+      </c>
+      <c r="B92" s="3">
+        <v>46096</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D92" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E92" s="4">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F92" s="5">
+        <f>IF(E92&gt;D92,E92-D92,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D92-E92),""))</f>
+        <v>0.14583333333333326</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="23" t="str">
+        <f>IF(ISNUMBER(B93),LEFT(TEXT(B93,"TTTT"),2)&amp;".","")</f>
+        <v/>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="23"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="5" t="str">
+        <f>IF(E93&gt;D93,E93-D93,IF(ISNUMBER(Stundenliste[[#This Row],[Von]]),"24:00"-(D93-E93),""))</f>
+        <v/>
+      </c>
+      <c r="G93" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -4654,20 +4837,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ReferenceId xmlns="d9f85066-e658-4e34-914c-f198c2427564" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4815,6 +4998,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57E083A2-B59E-4178-BBDB-6F72551558F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -4828,14 +5019,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="becce21f-4543-4ee3-84d8-746b4cf7c34b"/>
     <ds:schemaRef ds:uri="d9f85066-e658-4e34-914c-f198c2427564"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A879EED-63D4-4BD6-ABDC-8DEB19CAAEDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
